--- a/data/exports/accounts_closed_merged.xlsx
+++ b/data/exports/accounts_closed_merged.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,74 +413,74 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V519"/>
+  <dimension ref="A1:V537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="n">
+      <c r="A1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="D1" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="E1" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="F1" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="G1" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="H1" t="n">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="I1" t="n">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="J1" t="n">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="K1" t="n">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="L1" t="n">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="M1" t="n">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="N1" t="n">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="O1" t="n">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="P1" t="n">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="Q1" t="n">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="R1" t="n">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="S1" t="n">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="T1" t="n">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="U1" t="n">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="n">
+      <c r="V1" t="n">
         <v>21</v>
       </c>
     </row>
@@ -19193,21 +19181,21 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Bahu SO</t>
+          <t>Badli SO Jhajjar</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>12414201</v>
+        <v>12410501</v>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr"/>
-      <c r="F447" t="inlineStr"/>
+      <c r="F447" t="n">
+        <v>1</v>
+      </c>
       <c r="G447" t="inlineStr"/>
       <c r="H447" t="inlineStr"/>
-      <c r="I447" t="n">
-        <v>3</v>
-      </c>
+      <c r="I447" t="inlineStr"/>
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr"/>
       <c r="L447" t="inlineStr"/>
@@ -19225,27 +19213,19 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Bajidpur Tappa Haveli BO</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>N9276</t>
-        </is>
-      </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>Nehru College Jhajjar SO</t>
-        </is>
-      </c>
+          <t>Bahadurgarh Mandi SO</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>12450801</v>
+      </c>
+      <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="inlineStr"/>
       <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr"/>
-      <c r="I448" t="n">
-        <v>1</v>
-      </c>
+      <c r="I448" t="inlineStr"/>
       <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr"/>
       <c r="L448" t="inlineStr"/>
@@ -19256,18 +19236,20 @@
       <c r="Q448" t="inlineStr"/>
       <c r="R448" t="inlineStr"/>
       <c r="S448" t="inlineStr"/>
-      <c r="T448" t="inlineStr"/>
+      <c r="T448" t="n">
+        <v>1</v>
+      </c>
       <c r="U448" t="inlineStr"/>
       <c r="V448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Beri SO</t>
+          <t>Bahadurgarh Sector 6 SO</t>
         </is>
       </c>
       <c r="B449" t="n">
-        <v>12420101</v>
+        <v>12450702</v>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr"/>
@@ -19275,49 +19257,43 @@
       <c r="F449" t="inlineStr"/>
       <c r="G449" t="inlineStr"/>
       <c r="H449" t="inlineStr"/>
-      <c r="I449" t="inlineStr"/>
+      <c r="I449" t="n">
+        <v>1</v>
+      </c>
       <c r="J449" t="inlineStr"/>
       <c r="K449" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L449" t="inlineStr"/>
       <c r="M449" t="inlineStr"/>
-      <c r="N449" t="n">
-        <v>1</v>
-      </c>
+      <c r="N449" t="inlineStr"/>
       <c r="O449" t="inlineStr"/>
       <c r="P449" t="inlineStr"/>
       <c r="Q449" t="inlineStr"/>
       <c r="R449" t="inlineStr"/>
       <c r="S449" t="inlineStr"/>
-      <c r="T449" t="n">
-        <v>1</v>
-      </c>
+      <c r="T449" t="inlineStr"/>
       <c r="U449" t="inlineStr"/>
       <c r="V449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Bishan BO</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>A3311</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>Beri SO</t>
-        </is>
-      </c>
+          <t>Charra SO</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>12450401</v>
+      </c>
+      <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr"/>
       <c r="F450" t="inlineStr"/>
       <c r="G450" t="inlineStr"/>
       <c r="H450" t="inlineStr"/>
-      <c r="I450" t="inlineStr"/>
+      <c r="I450" t="n">
+        <v>4</v>
+      </c>
       <c r="J450" t="inlineStr"/>
       <c r="K450" t="n">
         <v>2</v>
@@ -19337,21 +19313,25 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Court Complex Jhajjar SO</t>
-        </is>
-      </c>
-      <c r="B451" t="n">
-        <v>12410301</v>
-      </c>
-      <c r="C451" t="inlineStr"/>
+          <t>Gandhra BO</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>L5370</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Sampla SO</t>
+        </is>
+      </c>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr"/>
       <c r="H451" t="inlineStr"/>
-      <c r="I451" t="n">
-        <v>1</v>
-      </c>
+      <c r="I451" t="inlineStr"/>
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="n">
         <v>1</v>
@@ -19371,11 +19351,11 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Dhakla SO</t>
+          <t>Hassangarh SO</t>
         </is>
       </c>
       <c r="B452" t="n">
-        <v>12410901</v>
+        <v>12440401</v>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr"/>
@@ -19385,7 +19365,9 @@
       </c>
       <c r="G452" t="inlineStr"/>
       <c r="H452" t="inlineStr"/>
-      <c r="I452" t="inlineStr"/>
+      <c r="I452" t="n">
+        <v>1</v>
+      </c>
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="n">
         <v>1</v>
@@ -19405,24 +19387,28 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Dighal SO</t>
-        </is>
-      </c>
-      <c r="B453" t="n">
-        <v>12410701</v>
-      </c>
-      <c r="C453" t="inlineStr"/>
+          <t>Ladout BO</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>J7280</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Bhalaut SO</t>
+        </is>
+      </c>
       <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr"/>
       <c r="G453" t="inlineStr"/>
       <c r="H453" t="inlineStr"/>
-      <c r="I453" t="n">
-        <v>2</v>
-      </c>
+      <c r="I453" t="inlineStr"/>
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L453" t="inlineStr"/>
       <c r="M453" t="inlineStr"/>
@@ -19439,11 +19425,11 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Dubaldhan SO</t>
+          <t>Main Bazar Bahadurgarh  SO</t>
         </is>
       </c>
       <c r="B454" t="n">
-        <v>12420201</v>
+        <v>12450705</v>
       </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr"/>
@@ -19451,12 +19437,10 @@
       <c r="F454" t="inlineStr"/>
       <c r="G454" t="inlineStr"/>
       <c r="H454" t="inlineStr"/>
-      <c r="I454" t="n">
-        <v>1</v>
-      </c>
+      <c r="I454" t="inlineStr"/>
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L454" t="inlineStr"/>
       <c r="M454" t="inlineStr"/>
@@ -19473,22 +19457,30 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Dujana SO</t>
-        </is>
-      </c>
-      <c r="B455" t="n">
-        <v>12410201</v>
-      </c>
-      <c r="C455" t="inlineStr"/>
+          <t>Maina BO</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>J7020</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Asthal Bohar SO</t>
+        </is>
+      </c>
       <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr"/>
       <c r="F455" t="inlineStr"/>
       <c r="G455" t="inlineStr"/>
       <c r="H455" t="inlineStr"/>
-      <c r="I455" t="inlineStr"/>
+      <c r="I455" t="n">
+        <v>1</v>
+      </c>
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L455" t="inlineStr"/>
       <c r="M455" t="inlineStr"/>
@@ -19505,25 +19497,23 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Gochhi BO</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>H3218</t>
-        </is>
-      </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>Dighal SO</t>
-        </is>
-      </c>
+          <t>Mandothi SO</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>12450601</v>
+      </c>
+      <c r="C456" t="inlineStr"/>
       <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr"/>
       <c r="F456" t="inlineStr"/>
       <c r="G456" t="inlineStr"/>
-      <c r="H456" t="inlineStr"/>
-      <c r="I456" t="inlineStr"/>
+      <c r="H456" t="n">
+        <v>1</v>
+      </c>
+      <c r="I456" t="n">
+        <v>1</v>
+      </c>
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="n">
         <v>1</v>
@@ -19543,17 +19533,17 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Jahazgarh BO</t>
+          <t>Pehrawar BO</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>A4293</t>
+          <t>J7021</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Jhajjar SO</t>
+          <t>Asthal Bohar SO</t>
         </is>
       </c>
       <c r="D457" t="inlineStr"/>
@@ -19564,7 +19554,7 @@
       <c r="I457" t="inlineStr"/>
       <c r="J457" t="inlineStr"/>
       <c r="K457" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L457" t="inlineStr"/>
       <c r="M457" t="inlineStr"/>
@@ -19581,55 +19571,55 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Jhajjar SO</t>
-        </is>
-      </c>
-      <c r="B458" t="n">
-        <v>12410302</v>
-      </c>
-      <c r="C458" t="inlineStr"/>
+          <t>Pelpa BO</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>L6162</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Badli SO Jhajjar</t>
+        </is>
+      </c>
       <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr"/>
       <c r="F458" t="inlineStr"/>
       <c r="G458" t="inlineStr"/>
       <c r="H458" t="inlineStr"/>
       <c r="I458" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J458" t="inlineStr"/>
-      <c r="K458" t="n">
-        <v>10</v>
-      </c>
+      <c r="K458" t="inlineStr"/>
       <c r="L458" t="inlineStr"/>
       <c r="M458" t="inlineStr"/>
       <c r="N458" t="inlineStr"/>
       <c r="O458" t="inlineStr"/>
       <c r="P458" t="inlineStr"/>
       <c r="Q458" t="inlineStr"/>
-      <c r="R458" t="n">
-        <v>1</v>
-      </c>
+      <c r="R458" t="inlineStr"/>
       <c r="S458" t="inlineStr"/>
       <c r="T458" t="inlineStr"/>
       <c r="U458" t="inlineStr"/>
-      <c r="V458" t="n">
-        <v>1</v>
-      </c>
+      <c r="V458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Khungai BO</t>
+          <t>Rewari Khera BO</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>N9282</t>
+          <t>H0669</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Nehru College Jhajjar SO</t>
+          <t>Charra SO</t>
         </is>
       </c>
       <c r="D459" t="inlineStr"/>
@@ -19657,11 +19647,11 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Machrauli SO</t>
+          <t>Sampla SO</t>
         </is>
       </c>
       <c r="B460" t="n">
-        <v>12410801</v>
+        <v>12450101</v>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
@@ -19670,7 +19660,7 @@
       <c r="G460" t="inlineStr"/>
       <c r="H460" t="inlineStr"/>
       <c r="I460" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="n">
@@ -19684,24 +19674,26 @@
       <c r="Q460" t="inlineStr"/>
       <c r="R460" t="inlineStr"/>
       <c r="S460" t="inlineStr"/>
-      <c r="T460" t="inlineStr"/>
+      <c r="T460" t="n">
+        <v>1</v>
+      </c>
       <c r="U460" t="inlineStr"/>
       <c r="V460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Majra BO</t>
+          <t>Soldha BO</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>J7210</t>
+          <t>L9909</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Dubaldhan SO</t>
+          <t>Bahadurgarh Mandi SO</t>
         </is>
       </c>
       <c r="D461" t="inlineStr"/>
@@ -19710,7 +19702,7 @@
       <c r="G461" t="inlineStr"/>
       <c r="H461" t="inlineStr"/>
       <c r="I461" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr"/>
@@ -19729,63 +19721,85 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Mehem SO</t>
-        </is>
-      </c>
-      <c r="B462" t="n">
-        <v>12411201</v>
-      </c>
+          <t>Total:</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr"/>
       <c r="C462" t="inlineStr"/>
-      <c r="D462" t="inlineStr"/>
-      <c r="E462" t="inlineStr"/>
-      <c r="F462" t="inlineStr"/>
-      <c r="G462" t="inlineStr"/>
-      <c r="H462" t="inlineStr"/>
+      <c r="D462" t="n">
+        <v>0</v>
+      </c>
+      <c r="E462" t="n">
+        <v>0</v>
+      </c>
+      <c r="F462" t="n">
+        <v>2</v>
+      </c>
+      <c r="G462" t="n">
+        <v>0</v>
+      </c>
+      <c r="H462" t="n">
+        <v>1</v>
+      </c>
       <c r="I462" t="n">
+        <v>15</v>
+      </c>
+      <c r="J462" t="n">
+        <v>0</v>
+      </c>
+      <c r="K462" t="n">
+        <v>19</v>
+      </c>
+      <c r="L462" t="n">
+        <v>0</v>
+      </c>
+      <c r="M462" t="n">
+        <v>0</v>
+      </c>
+      <c r="N462" t="n">
+        <v>0</v>
+      </c>
+      <c r="O462" t="n">
+        <v>0</v>
+      </c>
+      <c r="P462" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q462" t="n">
+        <v>0</v>
+      </c>
+      <c r="R462" t="n">
+        <v>0</v>
+      </c>
+      <c r="S462" t="n">
+        <v>0</v>
+      </c>
+      <c r="T462" t="n">
         <v>2</v>
       </c>
-      <c r="J462" t="inlineStr"/>
-      <c r="K462" t="n">
-        <v>4</v>
-      </c>
-      <c r="L462" t="inlineStr"/>
-      <c r="M462" t="inlineStr"/>
-      <c r="N462" t="inlineStr"/>
-      <c r="O462" t="inlineStr"/>
-      <c r="P462" t="inlineStr"/>
-      <c r="Q462" t="inlineStr"/>
-      <c r="R462" t="inlineStr"/>
-      <c r="S462" t="inlineStr"/>
-      <c r="T462" t="n">
-        <v>1</v>
-      </c>
-      <c r="U462" t="inlineStr"/>
-      <c r="V462" t="inlineStr"/>
+      <c r="U462" t="n">
+        <v>0</v>
+      </c>
+      <c r="V462" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Mehrana BO</t>
-        </is>
-      </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>C0296</t>
-        </is>
-      </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>Dujana SO</t>
-        </is>
-      </c>
+          <t xml:space="preserve">
+Product Wise A/C Report
+</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr"/>
+      <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr"/>
       <c r="G463" t="inlineStr"/>
       <c r="H463" t="inlineStr"/>
-      <c r="I463" t="n">
-        <v>1</v>
-      </c>
+      <c r="I463" t="inlineStr"/>
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr"/>
       <c r="L463" t="inlineStr"/>
@@ -19803,59 +19817,135 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Nehru College Jhajjar SO</t>
-        </is>
-      </c>
-      <c r="B464" t="n">
-        <v>12410401</v>
-      </c>
-      <c r="C464" t="inlineStr"/>
-      <c r="D464" t="inlineStr"/>
-      <c r="E464" t="inlineStr"/>
-      <c r="F464" t="inlineStr"/>
-      <c r="G464" t="inlineStr"/>
-      <c r="H464" t="inlineStr"/>
-      <c r="I464" t="inlineStr"/>
-      <c r="J464" t="inlineStr"/>
-      <c r="K464" t="n">
-        <v>1</v>
-      </c>
-      <c r="L464" t="inlineStr"/>
-      <c r="M464" t="inlineStr"/>
-      <c r="N464" t="inlineStr"/>
-      <c r="O464" t="inlineStr"/>
-      <c r="P464" t="inlineStr"/>
-      <c r="Q464" t="inlineStr"/>
-      <c r="R464" t="inlineStr"/>
-      <c r="S464" t="inlineStr"/>
-      <c r="T464" t="inlineStr"/>
-      <c r="U464" t="inlineStr"/>
-      <c r="V464" t="inlineStr"/>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>SOL ID / BOCODE</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>SO Name</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>NSS87</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>NSS92</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>MIS</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>PPFGP</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>SCSS</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>SANPG</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>SBBAS</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>SBSGP</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>SDIGP</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>SPNGP</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>PRFTS</t>
+        </is>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>KVN</t>
+        </is>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>KVP</t>
+        </is>
+      </c>
+      <c r="T464" t="inlineStr">
+        <is>
+          <t>NSC8</t>
+        </is>
+      </c>
+      <c r="U464" t="inlineStr">
+        <is>
+          <t>NSC9</t>
+        </is>
+      </c>
+      <c r="V464" t="inlineStr">
+        <is>
+          <t>MSSC</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Sahlawas SO</t>
+          <t>Bahu SO</t>
         </is>
       </c>
       <c r="B465" t="n">
-        <v>12414601</v>
+        <v>12414201</v>
       </c>
       <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr"/>
-      <c r="F465" t="n">
-        <v>3</v>
-      </c>
+      <c r="F465" t="inlineStr"/>
       <c r="G465" t="inlineStr"/>
       <c r="H465" t="inlineStr"/>
       <c r="I465" t="n">
         <v>3</v>
       </c>
       <c r="J465" t="inlineStr"/>
-      <c r="K465" t="n">
-        <v>6</v>
-      </c>
+      <c r="K465" t="inlineStr"/>
       <c r="L465" t="inlineStr"/>
       <c r="M465" t="inlineStr"/>
       <c r="N465" t="inlineStr"/>
@@ -19871,17 +19961,17 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Silana BO</t>
+          <t>Bajidpur Tappa Haveli BO</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>D7946</t>
+          <t>N9276</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Jhajjar SO</t>
+          <t>Nehru College Jhajjar SO</t>
         </is>
       </c>
       <c r="D466" t="inlineStr"/>
@@ -19909,79 +19999,55 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Total:</t>
-        </is>
-      </c>
-      <c r="B467" t="inlineStr"/>
+          <t>Beri SO</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>12420101</v>
+      </c>
       <c r="C467" t="inlineStr"/>
-      <c r="D467" t="n">
-        <v>0</v>
-      </c>
-      <c r="E467" t="n">
-        <v>0</v>
-      </c>
-      <c r="F467" t="n">
-        <v>4</v>
-      </c>
-      <c r="G467" t="n">
-        <v>0</v>
-      </c>
-      <c r="H467" t="n">
-        <v>0</v>
-      </c>
-      <c r="I467" t="n">
-        <v>25</v>
-      </c>
-      <c r="J467" t="n">
-        <v>0</v>
-      </c>
+      <c r="D467" t="inlineStr"/>
+      <c r="E467" t="inlineStr"/>
+      <c r="F467" t="inlineStr"/>
+      <c r="G467" t="inlineStr"/>
+      <c r="H467" t="inlineStr"/>
+      <c r="I467" t="inlineStr"/>
+      <c r="J467" t="inlineStr"/>
       <c r="K467" t="n">
-        <v>41</v>
-      </c>
-      <c r="L467" t="n">
-        <v>0</v>
-      </c>
-      <c r="M467" t="n">
-        <v>0</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L467" t="inlineStr"/>
+      <c r="M467" t="inlineStr"/>
       <c r="N467" t="n">
         <v>1</v>
       </c>
-      <c r="O467" t="n">
-        <v>0</v>
-      </c>
-      <c r="P467" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q467" t="n">
-        <v>0</v>
-      </c>
-      <c r="R467" t="n">
-        <v>1</v>
-      </c>
-      <c r="S467" t="n">
-        <v>0</v>
-      </c>
+      <c r="O467" t="inlineStr"/>
+      <c r="P467" t="inlineStr"/>
+      <c r="Q467" t="inlineStr"/>
+      <c r="R467" t="inlineStr"/>
+      <c r="S467" t="inlineStr"/>
       <c r="T467" t="n">
-        <v>2</v>
-      </c>
-      <c r="U467" t="n">
-        <v>0</v>
-      </c>
-      <c r="V467" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U467" t="inlineStr"/>
+      <c r="V467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Product Wise A/C Report
-</t>
-        </is>
-      </c>
-      <c r="B468" t="inlineStr"/>
-      <c r="C468" t="inlineStr"/>
+          <t>Bishan BO</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>A3311</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Beri SO</t>
+        </is>
+      </c>
       <c r="D468" t="inlineStr"/>
       <c r="E468" t="inlineStr"/>
       <c r="F468" t="inlineStr"/>
@@ -19989,7 +20055,9 @@
       <c r="H468" t="inlineStr"/>
       <c r="I468" t="inlineStr"/>
       <c r="J468" t="inlineStr"/>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="n">
+        <v>2</v>
+      </c>
       <c r="L468" t="inlineStr"/>
       <c r="M468" t="inlineStr"/>
       <c r="N468" t="inlineStr"/>
@@ -20005,141 +20073,59 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>SOL ID / BOCODE</t>
-        </is>
-      </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>SO Name</t>
-        </is>
-      </c>
-      <c r="D469" t="inlineStr">
-        <is>
-          <t>NSS87</t>
-        </is>
-      </c>
-      <c r="E469" t="inlineStr">
-        <is>
-          <t>NSS92</t>
-        </is>
-      </c>
-      <c r="F469" t="inlineStr">
-        <is>
-          <t>MIS</t>
-        </is>
-      </c>
-      <c r="G469" t="inlineStr">
-        <is>
-          <t>PPFGP</t>
-        </is>
-      </c>
-      <c r="H469" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="I469" t="inlineStr">
-        <is>
-          <t>RD</t>
-        </is>
-      </c>
-      <c r="J469" t="inlineStr">
-        <is>
-          <t>SCSS</t>
-        </is>
-      </c>
-      <c r="K469" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="L469" t="inlineStr">
-        <is>
-          <t>SANPG</t>
-        </is>
-      </c>
-      <c r="M469" t="inlineStr">
-        <is>
-          <t>SBBAS</t>
-        </is>
-      </c>
-      <c r="N469" t="inlineStr">
-        <is>
-          <t>SBSGP</t>
-        </is>
-      </c>
-      <c r="O469" t="inlineStr">
-        <is>
-          <t>SDIGP</t>
-        </is>
-      </c>
-      <c r="P469" t="inlineStr">
-        <is>
-          <t>SPNGP</t>
-        </is>
-      </c>
-      <c r="Q469" t="inlineStr">
-        <is>
-          <t>PRFTS</t>
-        </is>
-      </c>
-      <c r="R469" t="inlineStr">
-        <is>
-          <t>KVN</t>
-        </is>
-      </c>
-      <c r="S469" t="inlineStr">
-        <is>
-          <t>KVP</t>
-        </is>
-      </c>
-      <c r="T469" t="inlineStr">
-        <is>
-          <t>NSC8</t>
-        </is>
-      </c>
-      <c r="U469" t="inlineStr">
-        <is>
-          <t>NSC9</t>
-        </is>
-      </c>
-      <c r="V469" t="inlineStr">
-        <is>
-          <t>MSSC</t>
-        </is>
-      </c>
+          <t>Court Complex Jhajjar SO</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>12410301</v>
+      </c>
+      <c r="C469" t="inlineStr"/>
+      <c r="D469" t="inlineStr"/>
+      <c r="E469" t="inlineStr"/>
+      <c r="F469" t="inlineStr"/>
+      <c r="G469" t="inlineStr"/>
+      <c r="H469" t="inlineStr"/>
+      <c r="I469" t="n">
+        <v>1</v>
+      </c>
+      <c r="J469" t="inlineStr"/>
+      <c r="K469" t="n">
+        <v>1</v>
+      </c>
+      <c r="L469" t="inlineStr"/>
+      <c r="M469" t="inlineStr"/>
+      <c r="N469" t="inlineStr"/>
+      <c r="O469" t="inlineStr"/>
+      <c r="P469" t="inlineStr"/>
+      <c r="Q469" t="inlineStr"/>
+      <c r="R469" t="inlineStr"/>
+      <c r="S469" t="inlineStr"/>
+      <c r="T469" t="inlineStr"/>
+      <c r="U469" t="inlineStr"/>
+      <c r="V469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Baland BO</t>
-        </is>
-      </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>O0155</t>
-        </is>
-      </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>Police Training Center Sunaria SO</t>
-        </is>
-      </c>
+          <t>Dhakla SO</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>12410901</v>
+      </c>
+      <c r="C470" t="inlineStr"/>
       <c r="D470" t="inlineStr"/>
       <c r="E470" t="inlineStr"/>
-      <c r="F470" t="inlineStr"/>
+      <c r="F470" t="n">
+        <v>1</v>
+      </c>
       <c r="G470" t="inlineStr"/>
       <c r="H470" t="inlineStr"/>
-      <c r="I470" t="n">
-        <v>2</v>
-      </c>
+      <c r="I470" t="inlineStr"/>
       <c r="J470" t="inlineStr"/>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="n">
+        <v>1</v>
+      </c>
       <c r="L470" t="inlineStr"/>
       <c r="M470" t="inlineStr"/>
       <c r="N470" t="inlineStr"/>
@@ -20155,25 +20141,21 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Chandi BO</t>
-        </is>
-      </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>F3581</t>
-        </is>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>Lakhan Majra SO</t>
-        </is>
-      </c>
+          <t>Dighal SO</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>12410701</v>
+      </c>
+      <c r="C471" t="inlineStr"/>
       <c r="D471" t="inlineStr"/>
       <c r="E471" t="inlineStr"/>
       <c r="F471" t="inlineStr"/>
       <c r="G471" t="inlineStr"/>
       <c r="H471" t="inlineStr"/>
-      <c r="I471" t="inlineStr"/>
+      <c r="I471" t="n">
+        <v>2</v>
+      </c>
       <c r="J471" t="inlineStr"/>
       <c r="K471" t="n">
         <v>3</v>
@@ -20193,19 +20175,13 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Chimni BO</t>
-        </is>
-      </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>J8915</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>Kahnaur SO</t>
-        </is>
-      </c>
+          <t>Dubaldhan SO</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>12420201</v>
+      </c>
+      <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr"/>
       <c r="F472" t="inlineStr"/>
@@ -20215,7 +20191,9 @@
         <v>1</v>
       </c>
       <c r="J472" t="inlineStr"/>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="n">
+        <v>3</v>
+      </c>
       <c r="L472" t="inlineStr"/>
       <c r="M472" t="inlineStr"/>
       <c r="N472" t="inlineStr"/>
@@ -20231,11 +20209,11 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Gandhi Camp SO</t>
+          <t>Dujana SO</t>
         </is>
       </c>
       <c r="B473" t="n">
-        <v>12400102</v>
+        <v>12410201</v>
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr"/>
@@ -20243,12 +20221,10 @@
       <c r="F473" t="inlineStr"/>
       <c r="G473" t="inlineStr"/>
       <c r="H473" t="inlineStr"/>
-      <c r="I473" t="n">
-        <v>2</v>
-      </c>
+      <c r="I473" t="inlineStr"/>
       <c r="J473" t="inlineStr"/>
       <c r="K473" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L473" t="inlineStr"/>
       <c r="M473" t="inlineStr"/>
@@ -20265,24 +20241,28 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Janta Colony Rohtak SO</t>
-        </is>
-      </c>
-      <c r="B474" t="n">
-        <v>12400104</v>
-      </c>
-      <c r="C474" t="inlineStr"/>
+          <t>Gochhi BO</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>H3218</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Dighal SO</t>
+        </is>
+      </c>
       <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr"/>
       <c r="F474" t="inlineStr"/>
       <c r="G474" t="inlineStr"/>
       <c r="H474" t="inlineStr"/>
-      <c r="I474" t="n">
-        <v>1</v>
-      </c>
+      <c r="I474" t="inlineStr"/>
       <c r="J474" t="inlineStr"/>
       <c r="K474" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L474" t="inlineStr"/>
       <c r="M474" t="inlineStr"/>
@@ -20290,26 +20270,28 @@
       <c r="O474" t="inlineStr"/>
       <c r="P474" t="inlineStr"/>
       <c r="Q474" t="inlineStr"/>
-      <c r="R474" t="n">
-        <v>1</v>
-      </c>
+      <c r="R474" t="inlineStr"/>
       <c r="S474" t="inlineStr"/>
-      <c r="T474" t="n">
-        <v>2</v>
-      </c>
+      <c r="T474" t="inlineStr"/>
       <c r="U474" t="inlineStr"/>
       <c r="V474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Kahnaur SO</t>
-        </is>
-      </c>
-      <c r="B475" t="n">
-        <v>12441201</v>
-      </c>
-      <c r="C475" t="inlineStr"/>
+          <t>Jahazgarh BO</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>A4293</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Jhajjar SO</t>
+        </is>
+      </c>
       <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr"/>
       <c r="F475" t="inlineStr"/>
@@ -20318,7 +20300,7 @@
       <c r="I475" t="inlineStr"/>
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L475" t="inlineStr"/>
       <c r="M475" t="inlineStr"/>
@@ -20335,11 +20317,11 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Kansala SO</t>
+          <t>Jhajjar SO</t>
         </is>
       </c>
       <c r="B476" t="n">
-        <v>12440601</v>
+        <v>12410302</v>
       </c>
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr"/>
@@ -20348,36 +20330,42 @@
       <c r="G476" t="inlineStr"/>
       <c r="H476" t="inlineStr"/>
       <c r="I476" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J476" t="inlineStr"/>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="n">
+        <v>10</v>
+      </c>
       <c r="L476" t="inlineStr"/>
       <c r="M476" t="inlineStr"/>
       <c r="N476" t="inlineStr"/>
       <c r="O476" t="inlineStr"/>
       <c r="P476" t="inlineStr"/>
       <c r="Q476" t="inlineStr"/>
-      <c r="R476" t="inlineStr"/>
+      <c r="R476" t="n">
+        <v>1</v>
+      </c>
       <c r="S476" t="inlineStr"/>
       <c r="T476" t="inlineStr"/>
       <c r="U476" t="inlineStr"/>
-      <c r="V476" t="inlineStr"/>
+      <c r="V476" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Khairari BO</t>
+          <t>Khungai BO</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>J2619</t>
+          <t>N9282</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Kalanaur SO Rohtak</t>
+          <t>Nehru College Jhajjar SO</t>
         </is>
       </c>
       <c r="D477" t="inlineStr"/>
@@ -20405,28 +20393,24 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Khidwali BO</t>
-        </is>
-      </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t>H9422</t>
-        </is>
-      </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>Sanghi SO</t>
-        </is>
-      </c>
+          <t>Machrauli SO</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>12410801</v>
+      </c>
+      <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr"/>
       <c r="F478" t="inlineStr"/>
       <c r="G478" t="inlineStr"/>
       <c r="H478" t="inlineStr"/>
-      <c r="I478" t="inlineStr"/>
+      <c r="I478" t="n">
+        <v>1</v>
+      </c>
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L478" t="inlineStr"/>
       <c r="M478" t="inlineStr"/>
@@ -20443,19 +20427,27 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Lakhan Majra SO</t>
-        </is>
-      </c>
-      <c r="B479" t="n">
-        <v>12451401</v>
-      </c>
-      <c r="C479" t="inlineStr"/>
+          <t>Majra BO</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>J7210</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Dubaldhan SO</t>
+        </is>
+      </c>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr"/>
       <c r="F479" t="inlineStr"/>
       <c r="G479" t="inlineStr"/>
       <c r="H479" t="inlineStr"/>
-      <c r="I479" t="inlineStr"/>
+      <c r="I479" t="n">
+        <v>1</v>
+      </c>
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr"/>
       <c r="L479" t="inlineStr"/>
@@ -20468,18 +20460,16 @@
       <c r="S479" t="inlineStr"/>
       <c r="T479" t="inlineStr"/>
       <c r="U479" t="inlineStr"/>
-      <c r="V479" t="n">
-        <v>1</v>
-      </c>
+      <c r="V479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Madina SO</t>
+          <t>Mehem SO</t>
         </is>
       </c>
       <c r="B480" t="n">
-        <v>12411101</v>
+        <v>12411201</v>
       </c>
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr"/>
@@ -20488,11 +20478,11 @@
       <c r="G480" t="inlineStr"/>
       <c r="H480" t="inlineStr"/>
       <c r="I480" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L480" t="inlineStr"/>
       <c r="M480" t="inlineStr"/>
@@ -20502,30 +20492,38 @@
       <c r="Q480" t="inlineStr"/>
       <c r="R480" t="inlineStr"/>
       <c r="S480" t="inlineStr"/>
-      <c r="T480" t="inlineStr"/>
+      <c r="T480" t="n">
+        <v>1</v>
+      </c>
       <c r="U480" t="inlineStr"/>
       <c r="V480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Model Town SO Rohtak</t>
-        </is>
-      </c>
-      <c r="B481" t="n">
-        <v>12400107</v>
-      </c>
-      <c r="C481" t="inlineStr"/>
+          <t>Mehrana BO</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>C0296</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Dujana SO</t>
+        </is>
+      </c>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr"/>
       <c r="F481" t="inlineStr"/>
       <c r="G481" t="inlineStr"/>
       <c r="H481" t="inlineStr"/>
-      <c r="I481" t="inlineStr"/>
+      <c r="I481" t="n">
+        <v>1</v>
+      </c>
       <c r="J481" t="inlineStr"/>
-      <c r="K481" t="n">
-        <v>3</v>
-      </c>
+      <c r="K481" t="inlineStr"/>
       <c r="L481" t="inlineStr"/>
       <c r="M481" t="inlineStr"/>
       <c r="N481" t="inlineStr"/>
@@ -20534,20 +20532,18 @@
       <c r="Q481" t="inlineStr"/>
       <c r="R481" t="inlineStr"/>
       <c r="S481" t="inlineStr"/>
-      <c r="T481" t="n">
-        <v>2</v>
-      </c>
+      <c r="T481" t="inlineStr"/>
       <c r="U481" t="inlineStr"/>
       <c r="V481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Mokhra SO</t>
+          <t>Nehru College Jhajjar SO</t>
         </is>
       </c>
       <c r="B482" t="n">
-        <v>12402201</v>
+        <v>12410401</v>
       </c>
       <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr"/>
@@ -20555,17 +20551,13 @@
       <c r="F482" t="inlineStr"/>
       <c r="G482" t="inlineStr"/>
       <c r="H482" t="inlineStr"/>
-      <c r="I482" t="n">
-        <v>1</v>
-      </c>
+      <c r="I482" t="inlineStr"/>
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="n">
         <v>1</v>
       </c>
       <c r="L482" t="inlineStr"/>
-      <c r="M482" t="n">
-        <v>1</v>
-      </c>
+      <c r="M482" t="inlineStr"/>
       <c r="N482" t="inlineStr"/>
       <c r="O482" t="inlineStr"/>
       <c r="P482" t="inlineStr"/>
@@ -20579,24 +20571,26 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Rohtak HO</t>
+          <t>Sahlawas SO</t>
         </is>
       </c>
       <c r="B483" t="n">
-        <v>12400100</v>
+        <v>12414601</v>
       </c>
       <c r="C483" t="inlineStr"/>
       <c r="D483" t="inlineStr"/>
       <c r="E483" t="inlineStr"/>
-      <c r="F483" t="inlineStr"/>
+      <c r="F483" t="n">
+        <v>3</v>
+      </c>
       <c r="G483" t="inlineStr"/>
       <c r="H483" t="inlineStr"/>
       <c r="I483" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J483" t="inlineStr"/>
       <c r="K483" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L483" t="inlineStr"/>
       <c r="M483" t="inlineStr"/>
@@ -20604,282 +20598,284 @@
       <c r="O483" t="inlineStr"/>
       <c r="P483" t="inlineStr"/>
       <c r="Q483" t="inlineStr"/>
-      <c r="R483" t="n">
-        <v>1</v>
-      </c>
+      <c r="R483" t="inlineStr"/>
       <c r="S483" t="inlineStr"/>
-      <c r="T483" t="n">
-        <v>2</v>
-      </c>
+      <c r="T483" t="inlineStr"/>
       <c r="U483" t="inlineStr"/>
       <c r="V483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Total:</t>
-        </is>
-      </c>
-      <c r="B484" t="inlineStr"/>
-      <c r="C484" t="inlineStr"/>
-      <c r="D484" t="n">
-        <v>0</v>
-      </c>
-      <c r="E484" t="n">
-        <v>0</v>
-      </c>
-      <c r="F484" t="n">
-        <v>0</v>
-      </c>
-      <c r="G484" t="n">
-        <v>0</v>
-      </c>
-      <c r="H484" t="n">
-        <v>0</v>
-      </c>
+          <t>Silana BO</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>D7946</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Jhajjar SO</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr"/>
+      <c r="E484" t="inlineStr"/>
+      <c r="F484" t="inlineStr"/>
+      <c r="G484" t="inlineStr"/>
+      <c r="H484" t="inlineStr"/>
       <c r="I484" t="n">
-        <v>37</v>
-      </c>
-      <c r="J484" t="n">
-        <v>0</v>
-      </c>
-      <c r="K484" t="n">
-        <v>29</v>
-      </c>
-      <c r="L484" t="n">
-        <v>0</v>
-      </c>
-      <c r="M484" t="n">
-        <v>1</v>
-      </c>
-      <c r="N484" t="n">
-        <v>0</v>
-      </c>
-      <c r="O484" t="n">
-        <v>0</v>
-      </c>
-      <c r="P484" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q484" t="n">
-        <v>0</v>
-      </c>
-      <c r="R484" t="n">
-        <v>2</v>
-      </c>
-      <c r="S484" t="n">
-        <v>0</v>
-      </c>
-      <c r="T484" t="n">
-        <v>6</v>
-      </c>
-      <c r="U484" t="n">
-        <v>0</v>
-      </c>
-      <c r="V484" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J484" t="inlineStr"/>
+      <c r="K484" t="inlineStr"/>
+      <c r="L484" t="inlineStr"/>
+      <c r="M484" t="inlineStr"/>
+      <c r="N484" t="inlineStr"/>
+      <c r="O484" t="inlineStr"/>
+      <c r="P484" t="inlineStr"/>
+      <c r="Q484" t="inlineStr"/>
+      <c r="R484" t="inlineStr"/>
+      <c r="S484" t="inlineStr"/>
+      <c r="T484" t="inlineStr"/>
+      <c r="U484" t="inlineStr"/>
+      <c r="V484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
+        <is>
+          <t>Total:</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr"/>
+      <c r="C485" t="inlineStr"/>
+      <c r="D485" t="n">
+        <v>0</v>
+      </c>
+      <c r="E485" t="n">
+        <v>0</v>
+      </c>
+      <c r="F485" t="n">
+        <v>4</v>
+      </c>
+      <c r="G485" t="n">
+        <v>0</v>
+      </c>
+      <c r="H485" t="n">
+        <v>0</v>
+      </c>
+      <c r="I485" t="n">
+        <v>25</v>
+      </c>
+      <c r="J485" t="n">
+        <v>0</v>
+      </c>
+      <c r="K485" t="n">
+        <v>41</v>
+      </c>
+      <c r="L485" t="n">
+        <v>0</v>
+      </c>
+      <c r="M485" t="n">
+        <v>0</v>
+      </c>
+      <c r="N485" t="n">
+        <v>1</v>
+      </c>
+      <c r="O485" t="n">
+        <v>0</v>
+      </c>
+      <c r="P485" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q485" t="n">
+        <v>0</v>
+      </c>
+      <c r="R485" t="n">
+        <v>1</v>
+      </c>
+      <c r="S485" t="n">
+        <v>0</v>
+      </c>
+      <c r="T485" t="n">
+        <v>2</v>
+      </c>
+      <c r="U485" t="n">
+        <v>0</v>
+      </c>
+      <c r="V485" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Product Wise A/C Report
 </t>
         </is>
       </c>
-      <c r="B485" t="inlineStr"/>
-      <c r="C485" t="inlineStr"/>
-      <c r="D485" t="inlineStr"/>
-      <c r="E485" t="inlineStr"/>
-      <c r="F485" t="inlineStr"/>
-      <c r="G485" t="inlineStr"/>
-      <c r="H485" t="inlineStr"/>
-      <c r="I485" t="inlineStr"/>
-      <c r="J485" t="inlineStr"/>
-      <c r="K485" t="inlineStr"/>
-      <c r="L485" t="inlineStr"/>
-      <c r="M485" t="inlineStr"/>
-      <c r="N485" t="inlineStr"/>
-      <c r="O485" t="inlineStr"/>
-      <c r="P485" t="inlineStr"/>
-      <c r="Q485" t="inlineStr"/>
-      <c r="R485" t="inlineStr"/>
-      <c r="S485" t="inlineStr"/>
-      <c r="T485" t="inlineStr"/>
-      <c r="U485" t="inlineStr"/>
-      <c r="V485" t="inlineStr"/>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>SOL ID / BOCODE</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>SO Name</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>NSS87</t>
-        </is>
-      </c>
-      <c r="E486" t="inlineStr">
-        <is>
-          <t>NSS92</t>
-        </is>
-      </c>
-      <c r="F486" t="inlineStr">
-        <is>
-          <t>MIS</t>
-        </is>
-      </c>
-      <c r="G486" t="inlineStr">
-        <is>
-          <t>PPFGP</t>
-        </is>
-      </c>
-      <c r="H486" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="I486" t="inlineStr">
-        <is>
-          <t>RD</t>
-        </is>
-      </c>
-      <c r="J486" t="inlineStr">
-        <is>
-          <t>SCSS</t>
-        </is>
-      </c>
-      <c r="K486" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="L486" t="inlineStr">
-        <is>
-          <t>SANPG</t>
-        </is>
-      </c>
-      <c r="M486" t="inlineStr">
-        <is>
-          <t>SBBAS</t>
-        </is>
-      </c>
-      <c r="N486" t="inlineStr">
-        <is>
-          <t>SBSGP</t>
-        </is>
-      </c>
-      <c r="O486" t="inlineStr">
-        <is>
-          <t>SDIGP</t>
-        </is>
-      </c>
-      <c r="P486" t="inlineStr">
-        <is>
-          <t>SPNGP</t>
-        </is>
-      </c>
-      <c r="Q486" t="inlineStr">
-        <is>
-          <t>PRFTS</t>
-        </is>
-      </c>
-      <c r="R486" t="inlineStr">
-        <is>
-          <t>KVN</t>
-        </is>
-      </c>
-      <c r="S486" t="inlineStr">
-        <is>
-          <t>KVP</t>
-        </is>
-      </c>
-      <c r="T486" t="inlineStr">
-        <is>
-          <t>NSC8</t>
-        </is>
-      </c>
-      <c r="U486" t="inlineStr">
-        <is>
-          <t>NSC9</t>
-        </is>
-      </c>
-      <c r="V486" t="inlineStr">
-        <is>
-          <t>MSSC</t>
-        </is>
-      </c>
+      <c r="B486" t="inlineStr"/>
+      <c r="C486" t="inlineStr"/>
+      <c r="D486" t="inlineStr"/>
+      <c r="E486" t="inlineStr"/>
+      <c r="F486" t="inlineStr"/>
+      <c r="G486" t="inlineStr"/>
+      <c r="H486" t="inlineStr"/>
+      <c r="I486" t="inlineStr"/>
+      <c r="J486" t="inlineStr"/>
+      <c r="K486" t="inlineStr"/>
+      <c r="L486" t="inlineStr"/>
+      <c r="M486" t="inlineStr"/>
+      <c r="N486" t="inlineStr"/>
+      <c r="O486" t="inlineStr"/>
+      <c r="P486" t="inlineStr"/>
+      <c r="Q486" t="inlineStr"/>
+      <c r="R486" t="inlineStr"/>
+      <c r="S486" t="inlineStr"/>
+      <c r="T486" t="inlineStr"/>
+      <c r="U486" t="inlineStr"/>
+      <c r="V486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Banwasa BO</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>J8898</t>
+          <t>SOL ID / BOCODE</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Baroda SO</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr"/>
-      <c r="E487" t="inlineStr"/>
-      <c r="F487" t="inlineStr"/>
-      <c r="G487" t="inlineStr"/>
-      <c r="H487" t="inlineStr"/>
-      <c r="I487" t="inlineStr"/>
-      <c r="J487" t="inlineStr"/>
-      <c r="K487" t="n">
-        <v>1</v>
-      </c>
-      <c r="L487" t="inlineStr"/>
-      <c r="M487" t="inlineStr"/>
-      <c r="N487" t="inlineStr"/>
-      <c r="O487" t="inlineStr"/>
-      <c r="P487" t="inlineStr"/>
-      <c r="Q487" t="inlineStr"/>
-      <c r="R487" t="inlineStr"/>
-      <c r="S487" t="inlineStr"/>
-      <c r="T487" t="inlineStr"/>
-      <c r="U487" t="inlineStr"/>
-      <c r="V487" t="inlineStr"/>
+          <t>SO Name</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>NSS87</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>NSS92</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>MIS</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>PPFGP</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>SCSS</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>SANPG</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>SBBAS</t>
+        </is>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>SBSGP</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>SDIGP</t>
+        </is>
+      </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>SPNGP</t>
+        </is>
+      </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>PRFTS</t>
+        </is>
+      </c>
+      <c r="R487" t="inlineStr">
+        <is>
+          <t>KVN</t>
+        </is>
+      </c>
+      <c r="S487" t="inlineStr">
+        <is>
+          <t>KVP</t>
+        </is>
+      </c>
+      <c r="T487" t="inlineStr">
+        <is>
+          <t>NSC8</t>
+        </is>
+      </c>
+      <c r="U487" t="inlineStr">
+        <is>
+          <t>NSC9</t>
+        </is>
+      </c>
+      <c r="V487" t="inlineStr">
+        <is>
+          <t>MSSC</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Bhainswal Kalan SO</t>
-        </is>
-      </c>
-      <c r="B488" t="n">
-        <v>13140901</v>
-      </c>
-      <c r="C488" t="inlineStr"/>
+          <t>Baland BO</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>O0155</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Police Training Center Sunaria SO</t>
+        </is>
+      </c>
       <c r="D488" t="inlineStr"/>
       <c r="E488" t="inlineStr"/>
       <c r="F488" t="inlineStr"/>
       <c r="G488" t="inlineStr"/>
       <c r="H488" t="inlineStr"/>
-      <c r="I488" t="inlineStr"/>
+      <c r="I488" t="n">
+        <v>2</v>
+      </c>
       <c r="J488" t="inlineStr"/>
-      <c r="K488" t="n">
-        <v>1</v>
-      </c>
+      <c r="K488" t="inlineStr"/>
       <c r="L488" t="inlineStr"/>
       <c r="M488" t="inlineStr"/>
       <c r="N488" t="inlineStr"/>
@@ -20895,17 +20891,17 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Bidhal Pinana BO</t>
+          <t>Chandi BO</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>L4463</t>
+          <t>F3581</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Gohana SO</t>
+          <t>Lakhan Majra SO</t>
         </is>
       </c>
       <c r="D489" t="inlineStr"/>
@@ -20916,7 +20912,7 @@
       <c r="I489" t="inlineStr"/>
       <c r="J489" t="inlineStr"/>
       <c r="K489" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L489" t="inlineStr"/>
       <c r="M489" t="inlineStr"/>
@@ -20933,17 +20929,17 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Busana BO</t>
+          <t>Chimni BO</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>L6252</t>
+          <t>J8915</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Mundlana SO</t>
+          <t>Kahnaur SO</t>
         </is>
       </c>
       <c r="D490" t="inlineStr"/>
@@ -20951,14 +20947,14 @@
       <c r="F490" t="inlineStr"/>
       <c r="G490" t="inlineStr"/>
       <c r="H490" t="inlineStr"/>
-      <c r="I490" t="inlineStr"/>
+      <c r="I490" t="n">
+        <v>1</v>
+      </c>
       <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr"/>
       <c r="L490" t="inlineStr"/>
       <c r="M490" t="inlineStr"/>
-      <c r="N490" t="n">
-        <v>1</v>
-      </c>
+      <c r="N490" t="inlineStr"/>
       <c r="O490" t="inlineStr"/>
       <c r="P490" t="inlineStr"/>
       <c r="Q490" t="inlineStr"/>
@@ -20971,32 +20967,28 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Chhetra BO</t>
-        </is>
-      </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>L6253</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>Mundlana SO</t>
-        </is>
-      </c>
+          <t>Gandhi Camp SO</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>12400102</v>
+      </c>
+      <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="inlineStr"/>
       <c r="G491" t="inlineStr"/>
       <c r="H491" t="inlineStr"/>
-      <c r="I491" t="inlineStr"/>
+      <c r="I491" t="n">
+        <v>2</v>
+      </c>
       <c r="J491" t="inlineStr"/>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="n">
+        <v>4</v>
+      </c>
       <c r="L491" t="inlineStr"/>
       <c r="M491" t="inlineStr"/>
-      <c r="N491" t="n">
-        <v>1</v>
-      </c>
+      <c r="N491" t="inlineStr"/>
       <c r="O491" t="inlineStr"/>
       <c r="P491" t="inlineStr"/>
       <c r="Q491" t="inlineStr"/>
@@ -21009,49 +21001,49 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Garhwal BO</t>
-        </is>
-      </c>
-      <c r="B492" t="inlineStr">
-        <is>
-          <t>E1208</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>Butana SO</t>
-        </is>
-      </c>
+          <t>Janta Colony Rohtak SO</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>12400104</v>
+      </c>
+      <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr"/>
       <c r="F492" t="inlineStr"/>
       <c r="G492" t="inlineStr"/>
       <c r="H492" t="inlineStr"/>
       <c r="I492" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J492" t="inlineStr"/>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="n">
+        <v>3</v>
+      </c>
       <c r="L492" t="inlineStr"/>
       <c r="M492" t="inlineStr"/>
       <c r="N492" t="inlineStr"/>
       <c r="O492" t="inlineStr"/>
       <c r="P492" t="inlineStr"/>
       <c r="Q492" t="inlineStr"/>
-      <c r="R492" t="inlineStr"/>
+      <c r="R492" t="n">
+        <v>1</v>
+      </c>
       <c r="S492" t="inlineStr"/>
-      <c r="T492" t="inlineStr"/>
+      <c r="T492" t="n">
+        <v>2</v>
+      </c>
       <c r="U492" t="inlineStr"/>
       <c r="V492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Gohana Mandi SO</t>
+          <t>Kahnaur SO</t>
         </is>
       </c>
       <c r="B493" t="n">
-        <v>13130102</v>
+        <v>12441201</v>
       </c>
       <c r="C493" t="inlineStr"/>
       <c r="D493" t="inlineStr"/>
@@ -21059,9 +21051,7 @@
       <c r="F493" t="inlineStr"/>
       <c r="G493" t="inlineStr"/>
       <c r="H493" t="inlineStr"/>
-      <c r="I493" t="n">
-        <v>1</v>
-      </c>
+      <c r="I493" t="inlineStr"/>
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="n">
         <v>3</v>
@@ -21081,11 +21071,11 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Gohana SO</t>
+          <t>Kansala SO</t>
         </is>
       </c>
       <c r="B494" t="n">
-        <v>13130103</v>
+        <v>12440601</v>
       </c>
       <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr"/>
@@ -21093,11 +21083,11 @@
       <c r="F494" t="inlineStr"/>
       <c r="G494" t="inlineStr"/>
       <c r="H494" t="inlineStr"/>
-      <c r="I494" t="inlineStr"/>
+      <c r="I494" t="n">
+        <v>19</v>
+      </c>
       <c r="J494" t="inlineStr"/>
-      <c r="K494" t="n">
-        <v>5</v>
-      </c>
+      <c r="K494" t="inlineStr"/>
       <c r="L494" t="inlineStr"/>
       <c r="M494" t="inlineStr"/>
       <c r="N494" t="inlineStr"/>
@@ -21113,17 +21103,17 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Gopalpur BO</t>
+          <t>Khairari BO</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>J9554</t>
+          <t>J2619</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Kharkhauda SO</t>
+          <t>Kalanaur SO Rohtak</t>
         </is>
       </c>
       <c r="D495" t="inlineStr"/>
@@ -21131,14 +21121,14 @@
       <c r="F495" t="inlineStr"/>
       <c r="G495" t="inlineStr"/>
       <c r="H495" t="inlineStr"/>
-      <c r="I495" t="inlineStr"/>
+      <c r="I495" t="n">
+        <v>1</v>
+      </c>
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr"/>
       <c r="L495" t="inlineStr"/>
       <c r="M495" t="inlineStr"/>
-      <c r="N495" t="n">
-        <v>1</v>
-      </c>
+      <c r="N495" t="inlineStr"/>
       <c r="O495" t="inlineStr"/>
       <c r="P495" t="inlineStr"/>
       <c r="Q495" t="inlineStr"/>
@@ -21151,32 +21141,36 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Kharkhauda SO</t>
-        </is>
-      </c>
-      <c r="B496" t="n">
-        <v>13140201</v>
-      </c>
-      <c r="C496" t="inlineStr"/>
+          <t>Khidwali BO</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>H9422</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Sanghi SO</t>
+        </is>
+      </c>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr"/>
       <c r="F496" t="inlineStr"/>
       <c r="G496" t="inlineStr"/>
       <c r="H496" t="inlineStr"/>
-      <c r="I496" t="n">
-        <v>1</v>
-      </c>
+      <c r="I496" t="inlineStr"/>
       <c r="J496" t="inlineStr"/>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="n">
+        <v>2</v>
+      </c>
       <c r="L496" t="inlineStr"/>
       <c r="M496" t="inlineStr"/>
       <c r="N496" t="inlineStr"/>
       <c r="O496" t="inlineStr"/>
       <c r="P496" t="inlineStr"/>
       <c r="Q496" t="inlineStr"/>
-      <c r="R496" t="n">
-        <v>1</v>
-      </c>
+      <c r="R496" t="inlineStr"/>
       <c r="S496" t="inlineStr"/>
       <c r="T496" t="inlineStr"/>
       <c r="U496" t="inlineStr"/>
@@ -21185,19 +21179,13 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Saragthal BO</t>
-        </is>
-      </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>A7184</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>Kanyagurukul Khanpur SO</t>
-        </is>
-      </c>
+          <t>Lakhan Majra SO</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>12451401</v>
+      </c>
+      <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="inlineStr"/>
@@ -21208,9 +21196,7 @@
       <c r="K497" t="inlineStr"/>
       <c r="L497" t="inlineStr"/>
       <c r="M497" t="inlineStr"/>
-      <c r="N497" t="n">
-        <v>1</v>
-      </c>
+      <c r="N497" t="inlineStr"/>
       <c r="O497" t="inlineStr"/>
       <c r="P497" t="inlineStr"/>
       <c r="Q497" t="inlineStr"/>
@@ -21218,16 +21204,18 @@
       <c r="S497" t="inlineStr"/>
       <c r="T497" t="inlineStr"/>
       <c r="U497" t="inlineStr"/>
-      <c r="V497" t="inlineStr"/>
+      <c r="V497" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Sonipat HO</t>
+          <t>Madina SO</t>
         </is>
       </c>
       <c r="B498" t="n">
-        <v>13100100</v>
+        <v>12411101</v>
       </c>
       <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr"/>
@@ -21235,115 +21223,85 @@
       <c r="F498" t="inlineStr"/>
       <c r="G498" t="inlineStr"/>
       <c r="H498" t="inlineStr"/>
-      <c r="I498" t="inlineStr"/>
+      <c r="I498" t="n">
+        <v>6</v>
+      </c>
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L498" t="inlineStr"/>
       <c r="M498" t="inlineStr"/>
-      <c r="N498" t="n">
-        <v>1</v>
-      </c>
+      <c r="N498" t="inlineStr"/>
       <c r="O498" t="inlineStr"/>
       <c r="P498" t="inlineStr"/>
       <c r="Q498" t="inlineStr"/>
-      <c r="R498" t="n">
-        <v>1</v>
-      </c>
+      <c r="R498" t="inlineStr"/>
       <c r="S498" t="inlineStr"/>
-      <c r="T498" t="n">
-        <v>3</v>
-      </c>
+      <c r="T498" t="inlineStr"/>
       <c r="U498" t="inlineStr"/>
       <c r="V498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Total:</t>
-        </is>
-      </c>
-      <c r="B499" t="inlineStr"/>
+          <t>Model Town SO Rohtak</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>12400107</v>
+      </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="n">
-        <v>0</v>
-      </c>
-      <c r="E499" t="n">
-        <v>0</v>
-      </c>
-      <c r="F499" t="n">
-        <v>0</v>
-      </c>
-      <c r="G499" t="n">
-        <v>0</v>
-      </c>
-      <c r="H499" t="n">
-        <v>0</v>
-      </c>
-      <c r="I499" t="n">
-        <v>4</v>
-      </c>
-      <c r="J499" t="n">
-        <v>0</v>
-      </c>
+      <c r="D499" t="inlineStr"/>
+      <c r="E499" t="inlineStr"/>
+      <c r="F499" t="inlineStr"/>
+      <c r="G499" t="inlineStr"/>
+      <c r="H499" t="inlineStr"/>
+      <c r="I499" t="inlineStr"/>
+      <c r="J499" t="inlineStr"/>
       <c r="K499" t="n">
-        <v>19</v>
-      </c>
-      <c r="L499" t="n">
-        <v>0</v>
-      </c>
-      <c r="M499" t="n">
-        <v>0</v>
-      </c>
-      <c r="N499" t="n">
-        <v>5</v>
-      </c>
-      <c r="O499" t="n">
-        <v>0</v>
-      </c>
-      <c r="P499" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q499" t="n">
-        <v>0</v>
-      </c>
-      <c r="R499" t="n">
+        <v>3</v>
+      </c>
+      <c r="L499" t="inlineStr"/>
+      <c r="M499" t="inlineStr"/>
+      <c r="N499" t="inlineStr"/>
+      <c r="O499" t="inlineStr"/>
+      <c r="P499" t="inlineStr"/>
+      <c r="Q499" t="inlineStr"/>
+      <c r="R499" t="inlineStr"/>
+      <c r="S499" t="inlineStr"/>
+      <c r="T499" t="n">
         <v>2</v>
       </c>
-      <c r="S499" t="n">
-        <v>0</v>
-      </c>
-      <c r="T499" t="n">
-        <v>3</v>
-      </c>
-      <c r="U499" t="n">
-        <v>0</v>
-      </c>
-      <c r="V499" t="n">
-        <v>0</v>
-      </c>
+      <c r="U499" t="inlineStr"/>
+      <c r="V499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Product Wise A/C Report
-</t>
-        </is>
-      </c>
-      <c r="B500" t="inlineStr"/>
+          <t>Mokhra SO</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>12402201</v>
+      </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr"/>
       <c r="F500" t="inlineStr"/>
       <c r="G500" t="inlineStr"/>
       <c r="H500" t="inlineStr"/>
-      <c r="I500" t="inlineStr"/>
+      <c r="I500" t="n">
+        <v>1</v>
+      </c>
       <c r="J500" t="inlineStr"/>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="n">
+        <v>1</v>
+      </c>
       <c r="L500" t="inlineStr"/>
-      <c r="M500" t="inlineStr"/>
+      <c r="M500" t="n">
+        <v>1</v>
+      </c>
       <c r="N500" t="inlineStr"/>
       <c r="O500" t="inlineStr"/>
       <c r="P500" t="inlineStr"/>
@@ -21357,162 +21315,116 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B501" t="inlineStr">
-        <is>
-          <t>SOL ID / BOCODE</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>SO Name</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>NSS87</t>
-        </is>
-      </c>
-      <c r="E501" t="inlineStr">
-        <is>
-          <t>NSS92</t>
-        </is>
-      </c>
-      <c r="F501" t="inlineStr">
-        <is>
-          <t>MIS</t>
-        </is>
-      </c>
-      <c r="G501" t="inlineStr">
-        <is>
-          <t>PPFGP</t>
-        </is>
-      </c>
-      <c r="H501" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="I501" t="inlineStr">
-        <is>
-          <t>RD</t>
-        </is>
-      </c>
-      <c r="J501" t="inlineStr">
-        <is>
-          <t>SCSS</t>
-        </is>
-      </c>
-      <c r="K501" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="L501" t="inlineStr">
-        <is>
-          <t>SANPG</t>
-        </is>
-      </c>
-      <c r="M501" t="inlineStr">
-        <is>
-          <t>SBBAS</t>
-        </is>
-      </c>
-      <c r="N501" t="inlineStr">
-        <is>
-          <t>SBSGP</t>
-        </is>
-      </c>
-      <c r="O501" t="inlineStr">
-        <is>
-          <t>SDIGP</t>
-        </is>
-      </c>
-      <c r="P501" t="inlineStr">
-        <is>
-          <t>SPNGP</t>
-        </is>
-      </c>
-      <c r="Q501" t="inlineStr">
-        <is>
-          <t>PRFTS</t>
-        </is>
-      </c>
-      <c r="R501" t="inlineStr">
-        <is>
-          <t>KVN</t>
-        </is>
-      </c>
-      <c r="S501" t="inlineStr">
-        <is>
-          <t>KVP</t>
-        </is>
-      </c>
-      <c r="T501" t="inlineStr">
-        <is>
-          <t>NSC8</t>
-        </is>
-      </c>
-      <c r="U501" t="inlineStr">
-        <is>
-          <t>NSC9</t>
-        </is>
-      </c>
-      <c r="V501" t="inlineStr">
-        <is>
-          <t>MSSC</t>
-        </is>
-      </c>
+          <t>Rohtak HO</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>12400100</v>
+      </c>
+      <c r="C501" t="inlineStr"/>
+      <c r="D501" t="inlineStr"/>
+      <c r="E501" t="inlineStr"/>
+      <c r="F501" t="inlineStr"/>
+      <c r="G501" t="inlineStr"/>
+      <c r="H501" t="inlineStr"/>
+      <c r="I501" t="n">
+        <v>4</v>
+      </c>
+      <c r="J501" t="inlineStr"/>
+      <c r="K501" t="n">
+        <v>9</v>
+      </c>
+      <c r="L501" t="inlineStr"/>
+      <c r="M501" t="inlineStr"/>
+      <c r="N501" t="inlineStr"/>
+      <c r="O501" t="inlineStr"/>
+      <c r="P501" t="inlineStr"/>
+      <c r="Q501" t="inlineStr"/>
+      <c r="R501" t="n">
+        <v>1</v>
+      </c>
+      <c r="S501" t="inlineStr"/>
+      <c r="T501" t="n">
+        <v>2</v>
+      </c>
+      <c r="U501" t="inlineStr"/>
+      <c r="V501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>AhulanaGannur BO</t>
-        </is>
-      </c>
-      <c r="B502" t="inlineStr">
-        <is>
-          <t>A8170</t>
-        </is>
-      </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>Ganaur SO</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr"/>
-      <c r="E502" t="inlineStr"/>
-      <c r="F502" t="inlineStr"/>
-      <c r="G502" t="inlineStr"/>
-      <c r="H502" t="inlineStr"/>
-      <c r="I502" t="inlineStr"/>
-      <c r="J502" t="inlineStr"/>
+          <t>Total:</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr"/>
+      <c r="C502" t="inlineStr"/>
+      <c r="D502" t="n">
+        <v>0</v>
+      </c>
+      <c r="E502" t="n">
+        <v>0</v>
+      </c>
+      <c r="F502" t="n">
+        <v>0</v>
+      </c>
+      <c r="G502" t="n">
+        <v>0</v>
+      </c>
+      <c r="H502" t="n">
+        <v>0</v>
+      </c>
+      <c r="I502" t="n">
+        <v>37</v>
+      </c>
+      <c r="J502" t="n">
+        <v>0</v>
+      </c>
       <c r="K502" t="n">
-        <v>1</v>
-      </c>
-      <c r="L502" t="inlineStr"/>
-      <c r="M502" t="inlineStr"/>
-      <c r="N502" t="inlineStr"/>
-      <c r="O502" t="inlineStr"/>
-      <c r="P502" t="inlineStr"/>
-      <c r="Q502" t="inlineStr"/>
-      <c r="R502" t="inlineStr"/>
-      <c r="S502" t="inlineStr"/>
-      <c r="T502" t="inlineStr"/>
-      <c r="U502" t="inlineStr"/>
-      <c r="V502" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="L502" t="n">
+        <v>0</v>
+      </c>
+      <c r="M502" t="n">
+        <v>1</v>
+      </c>
+      <c r="N502" t="n">
+        <v>0</v>
+      </c>
+      <c r="O502" t="n">
+        <v>0</v>
+      </c>
+      <c r="P502" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>0</v>
+      </c>
+      <c r="R502" t="n">
+        <v>2</v>
+      </c>
+      <c r="S502" t="n">
+        <v>0</v>
+      </c>
+      <c r="T502" t="n">
+        <v>6</v>
+      </c>
+      <c r="U502" t="n">
+        <v>0</v>
+      </c>
+      <c r="V502" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Atlas Cycle SO</t>
-        </is>
-      </c>
-      <c r="B503" t="n">
-        <v>13100101</v>
-      </c>
+          <t xml:space="preserve">
+Product Wise A/C Report
+</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr"/>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr"/>
@@ -21521,9 +21433,7 @@
       <c r="H503" t="inlineStr"/>
       <c r="I503" t="inlineStr"/>
       <c r="J503" t="inlineStr"/>
-      <c r="K503" t="n">
-        <v>2</v>
-      </c>
+      <c r="K503" t="inlineStr"/>
       <c r="L503" t="inlineStr"/>
       <c r="M503" t="inlineStr"/>
       <c r="N503" t="inlineStr"/>
@@ -21539,45 +21449,131 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Bahalgarh SO</t>
-        </is>
-      </c>
-      <c r="B504" t="n">
-        <v>13102101</v>
-      </c>
-      <c r="C504" t="inlineStr"/>
-      <c r="D504" t="inlineStr"/>
-      <c r="E504" t="inlineStr"/>
-      <c r="F504" t="inlineStr"/>
-      <c r="G504" t="inlineStr"/>
-      <c r="H504" t="inlineStr"/>
-      <c r="I504" t="inlineStr"/>
-      <c r="J504" t="inlineStr"/>
-      <c r="K504" t="n">
-        <v>1</v>
-      </c>
-      <c r="L504" t="inlineStr"/>
-      <c r="M504" t="inlineStr"/>
-      <c r="N504" t="inlineStr"/>
-      <c r="O504" t="inlineStr"/>
-      <c r="P504" t="inlineStr"/>
-      <c r="Q504" t="inlineStr"/>
-      <c r="R504" t="inlineStr"/>
-      <c r="S504" t="inlineStr"/>
-      <c r="T504" t="inlineStr"/>
-      <c r="U504" t="inlineStr"/>
-      <c r="V504" t="inlineStr"/>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>SOL ID / BOCODE</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>SO Name</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>NSS87</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>NSS92</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>MIS</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>PPFGP</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>SCSS</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>SANPG</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>SBBAS</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>SBSGP</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>SDIGP</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>SPNGP</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>PRFTS</t>
+        </is>
+      </c>
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>KVN</t>
+        </is>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>KVP</t>
+        </is>
+      </c>
+      <c r="T504" t="inlineStr">
+        <is>
+          <t>NSC8</t>
+        </is>
+      </c>
+      <c r="U504" t="inlineStr">
+        <is>
+          <t>NSC9</t>
+        </is>
+      </c>
+      <c r="V504" t="inlineStr">
+        <is>
+          <t>MSSC</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Bhatgaon SO Sonipat</t>
-        </is>
-      </c>
-      <c r="B505" t="n">
-        <v>13102201</v>
-      </c>
-      <c r="C505" t="inlineStr"/>
+          <t>Banwasa BO</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>J8898</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Baroda SO</t>
+        </is>
+      </c>
       <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr"/>
       <c r="F505" t="inlineStr"/>
@@ -21603,11 +21599,11 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Ganaur City SO</t>
+          <t>Bhainswal Kalan SO</t>
         </is>
       </c>
       <c r="B506" t="n">
-        <v>13110101</v>
+        <v>13140901</v>
       </c>
       <c r="C506" t="inlineStr"/>
       <c r="D506" t="inlineStr"/>
@@ -21618,7 +21614,7 @@
       <c r="I506" t="inlineStr"/>
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L506" t="inlineStr"/>
       <c r="M506" t="inlineStr"/>
@@ -21635,13 +21631,19 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Ganaur SO</t>
-        </is>
-      </c>
-      <c r="B507" t="n">
-        <v>13110102</v>
-      </c>
-      <c r="C507" t="inlineStr"/>
+          <t>Bidhal Pinana BO</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>L4463</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Gohana SO</t>
+        </is>
+      </c>
       <c r="D507" t="inlineStr"/>
       <c r="E507" t="inlineStr"/>
       <c r="F507" t="inlineStr"/>
@@ -21650,7 +21652,7 @@
       <c r="I507" t="inlineStr"/>
       <c r="J507" t="inlineStr"/>
       <c r="K507" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L507" t="inlineStr"/>
       <c r="M507" t="inlineStr"/>
@@ -21667,13 +21669,19 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Gohana Road SO Sonipat</t>
-        </is>
-      </c>
-      <c r="B508" t="n">
-        <v>13100104</v>
-      </c>
-      <c r="C508" t="inlineStr"/>
+          <t>Busana BO</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>L6252</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Mundlana SO</t>
+        </is>
+      </c>
       <c r="D508" t="inlineStr"/>
       <c r="E508" t="inlineStr"/>
       <c r="F508" t="inlineStr"/>
@@ -21681,12 +21689,12 @@
       <c r="H508" t="inlineStr"/>
       <c r="I508" t="inlineStr"/>
       <c r="J508" t="inlineStr"/>
-      <c r="K508" t="n">
-        <v>1</v>
-      </c>
+      <c r="K508" t="inlineStr"/>
       <c r="L508" t="inlineStr"/>
       <c r="M508" t="inlineStr"/>
-      <c r="N508" t="inlineStr"/>
+      <c r="N508" t="n">
+        <v>1</v>
+      </c>
       <c r="O508" t="inlineStr"/>
       <c r="P508" t="inlineStr"/>
       <c r="Q508" t="inlineStr"/>
@@ -21699,13 +21707,19 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>HOUSING BOARD COLONY SONIPAT</t>
-        </is>
-      </c>
-      <c r="B509" t="n">
-        <v>13100105</v>
-      </c>
-      <c r="C509" t="inlineStr"/>
+          <t>Chhetra BO</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>L6253</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Mundlana SO</t>
+        </is>
+      </c>
       <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr"/>
       <c r="F509" t="inlineStr"/>
@@ -21716,32 +21730,32 @@
       <c r="K509" t="inlineStr"/>
       <c r="L509" t="inlineStr"/>
       <c r="M509" t="inlineStr"/>
-      <c r="N509" t="inlineStr"/>
+      <c r="N509" t="n">
+        <v>1</v>
+      </c>
       <c r="O509" t="inlineStr"/>
       <c r="P509" t="inlineStr"/>
       <c r="Q509" t="inlineStr"/>
       <c r="R509" t="inlineStr"/>
       <c r="S509" t="inlineStr"/>
-      <c r="T509" t="n">
-        <v>1</v>
-      </c>
+      <c r="T509" t="inlineStr"/>
       <c r="U509" t="inlineStr"/>
       <c r="V509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Joshi Chauhan B.O.</t>
+          <t>Garhwal BO</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>AO934</t>
+          <t>E1208</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Bahalgarh SO</t>
+          <t>Butana SO</t>
         </is>
       </c>
       <c r="D510" t="inlineStr"/>
@@ -21749,11 +21763,11 @@
       <c r="F510" t="inlineStr"/>
       <c r="G510" t="inlineStr"/>
       <c r="H510" t="inlineStr"/>
-      <c r="I510" t="inlineStr"/>
+      <c r="I510" t="n">
+        <v>2</v>
+      </c>
       <c r="J510" t="inlineStr"/>
-      <c r="K510" t="n">
-        <v>2</v>
-      </c>
+      <c r="K510" t="inlineStr"/>
       <c r="L510" t="inlineStr"/>
       <c r="M510" t="inlineStr"/>
       <c r="N510" t="inlineStr"/>
@@ -21769,11 +21783,11 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Juan SO</t>
+          <t>Gohana Mandi SO</t>
         </is>
       </c>
       <c r="B511" t="n">
-        <v>13102401</v>
+        <v>13130102</v>
       </c>
       <c r="C511" t="inlineStr"/>
       <c r="D511" t="inlineStr"/>
@@ -21785,7 +21799,9 @@
         <v>1</v>
       </c>
       <c r="J511" t="inlineStr"/>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="n">
+        <v>3</v>
+      </c>
       <c r="L511" t="inlineStr"/>
       <c r="M511" t="inlineStr"/>
       <c r="N511" t="inlineStr"/>
@@ -21801,29 +21817,23 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Mahra II BO</t>
-        </is>
-      </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>L8604</t>
-        </is>
-      </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>Juan SO</t>
-        </is>
-      </c>
+          <t>Gohana SO</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>13130103</v>
+      </c>
+      <c r="C512" t="inlineStr"/>
       <c r="D512" t="inlineStr"/>
       <c r="E512" t="inlineStr"/>
       <c r="F512" t="inlineStr"/>
       <c r="G512" t="inlineStr"/>
       <c r="H512" t="inlineStr"/>
-      <c r="I512" t="n">
-        <v>3</v>
-      </c>
+      <c r="I512" t="inlineStr"/>
       <c r="J512" t="inlineStr"/>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="n">
+        <v>5</v>
+      </c>
       <c r="L512" t="inlineStr"/>
       <c r="M512" t="inlineStr"/>
       <c r="N512" t="inlineStr"/>
@@ -21839,26 +21849,32 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Murthal SO</t>
-        </is>
-      </c>
-      <c r="B513" t="n">
-        <v>13102701</v>
-      </c>
-      <c r="C513" t="inlineStr"/>
+          <t>Gopalpur BO</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>J9554</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Kharkhauda SO</t>
+        </is>
+      </c>
       <c r="D513" t="inlineStr"/>
       <c r="E513" t="inlineStr"/>
       <c r="F513" t="inlineStr"/>
       <c r="G513" t="inlineStr"/>
       <c r="H513" t="inlineStr"/>
-      <c r="I513" t="n">
-        <v>1</v>
-      </c>
+      <c r="I513" t="inlineStr"/>
       <c r="J513" t="inlineStr"/>
       <c r="K513" t="inlineStr"/>
       <c r="L513" t="inlineStr"/>
       <c r="M513" t="inlineStr"/>
-      <c r="N513" t="inlineStr"/>
+      <c r="N513" t="n">
+        <v>1</v>
+      </c>
       <c r="O513" t="inlineStr"/>
       <c r="P513" t="inlineStr"/>
       <c r="Q513" t="inlineStr"/>
@@ -21871,11 +21887,11 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Rohat SO Sonipat</t>
+          <t>Kharkhauda SO</t>
         </is>
       </c>
       <c r="B514" t="n">
-        <v>13140301</v>
+        <v>13140201</v>
       </c>
       <c r="C514" t="inlineStr"/>
       <c r="D514" t="inlineStr"/>
@@ -21884,7 +21900,7 @@
       <c r="G514" t="inlineStr"/>
       <c r="H514" t="inlineStr"/>
       <c r="I514" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J514" t="inlineStr"/>
       <c r="K514" t="inlineStr"/>
@@ -21894,7 +21910,9 @@
       <c r="O514" t="inlineStr"/>
       <c r="P514" t="inlineStr"/>
       <c r="Q514" t="inlineStr"/>
-      <c r="R514" t="inlineStr"/>
+      <c r="R514" t="n">
+        <v>1</v>
+      </c>
       <c r="S514" t="inlineStr"/>
       <c r="T514" t="inlineStr"/>
       <c r="U514" t="inlineStr"/>
@@ -21903,17 +21921,17 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Sheikhpura BO</t>
+          <t>Saragthal BO</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>E1661</t>
+          <t>A7184</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Ganaur SO</t>
+          <t>Kanyagurukul Khanpur SO</t>
         </is>
       </c>
       <c r="D515" t="inlineStr"/>
@@ -21923,12 +21941,12 @@
       <c r="H515" t="inlineStr"/>
       <c r="I515" t="inlineStr"/>
       <c r="J515" t="inlineStr"/>
-      <c r="K515" t="n">
-        <v>2</v>
-      </c>
+      <c r="K515" t="inlineStr"/>
       <c r="L515" t="inlineStr"/>
       <c r="M515" t="inlineStr"/>
-      <c r="N515" t="inlineStr"/>
+      <c r="N515" t="n">
+        <v>1</v>
+      </c>
       <c r="O515" t="inlineStr"/>
       <c r="P515" t="inlineStr"/>
       <c r="Q515" t="inlineStr"/>
@@ -21941,11 +21959,11 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Sonipat Kty SO</t>
+          <t>Sonipat HO</t>
         </is>
       </c>
       <c r="B516" t="n">
-        <v>13100110</v>
+        <v>13100100</v>
       </c>
       <c r="C516" t="inlineStr"/>
       <c r="D516" t="inlineStr"/>
@@ -21953,64 +21971,104 @@
       <c r="F516" t="inlineStr"/>
       <c r="G516" t="inlineStr"/>
       <c r="H516" t="inlineStr"/>
-      <c r="I516" t="n">
-        <v>1</v>
-      </c>
+      <c r="I516" t="inlineStr"/>
       <c r="J516" t="inlineStr"/>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="n">
+        <v>3</v>
+      </c>
       <c r="L516" t="inlineStr"/>
       <c r="M516" t="inlineStr"/>
-      <c r="N516" t="inlineStr"/>
+      <c r="N516" t="n">
+        <v>1</v>
+      </c>
       <c r="O516" t="inlineStr"/>
       <c r="P516" t="inlineStr"/>
       <c r="Q516" t="inlineStr"/>
-      <c r="R516" t="inlineStr"/>
+      <c r="R516" t="n">
+        <v>1</v>
+      </c>
       <c r="S516" t="inlineStr"/>
-      <c r="T516" t="inlineStr"/>
+      <c r="T516" t="n">
+        <v>3</v>
+      </c>
       <c r="U516" t="inlineStr"/>
       <c r="V516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Sonipat Mandi SO</t>
-        </is>
-      </c>
-      <c r="B517" t="n">
-        <v>13100111</v>
-      </c>
+          <t>Total:</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr"/>
       <c r="C517" t="inlineStr"/>
-      <c r="D517" t="inlineStr"/>
-      <c r="E517" t="inlineStr"/>
-      <c r="F517" t="inlineStr"/>
-      <c r="G517" t="inlineStr"/>
-      <c r="H517" t="inlineStr"/>
-      <c r="I517" t="inlineStr"/>
-      <c r="J517" t="inlineStr"/>
+      <c r="D517" t="n">
+        <v>0</v>
+      </c>
+      <c r="E517" t="n">
+        <v>0</v>
+      </c>
+      <c r="F517" t="n">
+        <v>0</v>
+      </c>
+      <c r="G517" t="n">
+        <v>0</v>
+      </c>
+      <c r="H517" t="n">
+        <v>0</v>
+      </c>
+      <c r="I517" t="n">
+        <v>4</v>
+      </c>
+      <c r="J517" t="n">
+        <v>0</v>
+      </c>
       <c r="K517" t="n">
-        <v>1</v>
-      </c>
-      <c r="L517" t="inlineStr"/>
-      <c r="M517" t="inlineStr"/>
-      <c r="N517" t="inlineStr"/>
-      <c r="O517" t="inlineStr"/>
-      <c r="P517" t="inlineStr"/>
-      <c r="Q517" t="inlineStr"/>
-      <c r="R517" t="inlineStr"/>
-      <c r="S517" t="inlineStr"/>
-      <c r="T517" t="inlineStr"/>
-      <c r="U517" t="inlineStr"/>
-      <c r="V517" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="L517" t="n">
+        <v>0</v>
+      </c>
+      <c r="M517" t="n">
+        <v>0</v>
+      </c>
+      <c r="N517" t="n">
+        <v>5</v>
+      </c>
+      <c r="O517" t="n">
+        <v>0</v>
+      </c>
+      <c r="P517" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q517" t="n">
+        <v>0</v>
+      </c>
+      <c r="R517" t="n">
+        <v>2</v>
+      </c>
+      <c r="S517" t="n">
+        <v>0</v>
+      </c>
+      <c r="T517" t="n">
+        <v>3</v>
+      </c>
+      <c r="U517" t="n">
+        <v>0</v>
+      </c>
+      <c r="V517" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Sonipat Sector 14 SO</t>
-        </is>
-      </c>
-      <c r="B518" t="n">
-        <v>13100112</v>
-      </c>
+          <t xml:space="preserve">
+Product Wise A/C Report
+</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr"/>
       <c r="C518" t="inlineStr"/>
       <c r="D518" t="inlineStr"/>
       <c r="E518" t="inlineStr"/>
@@ -22019,9 +22077,7 @@
       <c r="H518" t="inlineStr"/>
       <c r="I518" t="inlineStr"/>
       <c r="J518" t="inlineStr"/>
-      <c r="K518" t="n">
-        <v>1</v>
-      </c>
+      <c r="K518" t="inlineStr"/>
       <c r="L518" t="inlineStr"/>
       <c r="M518" t="inlineStr"/>
       <c r="N518" t="inlineStr"/>
@@ -22030,75 +22086,755 @@
       <c r="Q518" t="inlineStr"/>
       <c r="R518" t="inlineStr"/>
       <c r="S518" t="inlineStr"/>
-      <c r="T518" t="n">
-        <v>1</v>
-      </c>
+      <c r="T518" t="inlineStr"/>
       <c r="U518" t="inlineStr"/>
       <c r="V518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>SOL ID / BOCODE</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>SO Name</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>NSS87</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>NSS92</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>MIS</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>PPFGP</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>SCSS</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>SANPG</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>SBBAS</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>SBSGP</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>SDIGP</t>
+        </is>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>SPNGP</t>
+        </is>
+      </c>
+      <c r="Q519" t="inlineStr">
+        <is>
+          <t>PRFTS</t>
+        </is>
+      </c>
+      <c r="R519" t="inlineStr">
+        <is>
+          <t>KVN</t>
+        </is>
+      </c>
+      <c r="S519" t="inlineStr">
+        <is>
+          <t>KVP</t>
+        </is>
+      </c>
+      <c r="T519" t="inlineStr">
+        <is>
+          <t>NSC8</t>
+        </is>
+      </c>
+      <c r="U519" t="inlineStr">
+        <is>
+          <t>NSC9</t>
+        </is>
+      </c>
+      <c r="V519" t="inlineStr">
+        <is>
+          <t>MSSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>AhulanaGannur BO</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>A8170</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Ganaur SO</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr"/>
+      <c r="E520" t="inlineStr"/>
+      <c r="F520" t="inlineStr"/>
+      <c r="G520" t="inlineStr"/>
+      <c r="H520" t="inlineStr"/>
+      <c r="I520" t="inlineStr"/>
+      <c r="J520" t="inlineStr"/>
+      <c r="K520" t="n">
+        <v>1</v>
+      </c>
+      <c r="L520" t="inlineStr"/>
+      <c r="M520" t="inlineStr"/>
+      <c r="N520" t="inlineStr"/>
+      <c r="O520" t="inlineStr"/>
+      <c r="P520" t="inlineStr"/>
+      <c r="Q520" t="inlineStr"/>
+      <c r="R520" t="inlineStr"/>
+      <c r="S520" t="inlineStr"/>
+      <c r="T520" t="inlineStr"/>
+      <c r="U520" t="inlineStr"/>
+      <c r="V520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Atlas Cycle SO</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>13100101</v>
+      </c>
+      <c r="C521" t="inlineStr"/>
+      <c r="D521" t="inlineStr"/>
+      <c r="E521" t="inlineStr"/>
+      <c r="F521" t="inlineStr"/>
+      <c r="G521" t="inlineStr"/>
+      <c r="H521" t="inlineStr"/>
+      <c r="I521" t="inlineStr"/>
+      <c r="J521" t="inlineStr"/>
+      <c r="K521" t="n">
+        <v>2</v>
+      </c>
+      <c r="L521" t="inlineStr"/>
+      <c r="M521" t="inlineStr"/>
+      <c r="N521" t="inlineStr"/>
+      <c r="O521" t="inlineStr"/>
+      <c r="P521" t="inlineStr"/>
+      <c r="Q521" t="inlineStr"/>
+      <c r="R521" t="inlineStr"/>
+      <c r="S521" t="inlineStr"/>
+      <c r="T521" t="inlineStr"/>
+      <c r="U521" t="inlineStr"/>
+      <c r="V521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Bahalgarh SO</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>13102101</v>
+      </c>
+      <c r="C522" t="inlineStr"/>
+      <c r="D522" t="inlineStr"/>
+      <c r="E522" t="inlineStr"/>
+      <c r="F522" t="inlineStr"/>
+      <c r="G522" t="inlineStr"/>
+      <c r="H522" t="inlineStr"/>
+      <c r="I522" t="inlineStr"/>
+      <c r="J522" t="inlineStr"/>
+      <c r="K522" t="n">
+        <v>1</v>
+      </c>
+      <c r="L522" t="inlineStr"/>
+      <c r="M522" t="inlineStr"/>
+      <c r="N522" t="inlineStr"/>
+      <c r="O522" t="inlineStr"/>
+      <c r="P522" t="inlineStr"/>
+      <c r="Q522" t="inlineStr"/>
+      <c r="R522" t="inlineStr"/>
+      <c r="S522" t="inlineStr"/>
+      <c r="T522" t="inlineStr"/>
+      <c r="U522" t="inlineStr"/>
+      <c r="V522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Bhatgaon SO Sonipat</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>13102201</v>
+      </c>
+      <c r="C523" t="inlineStr"/>
+      <c r="D523" t="inlineStr"/>
+      <c r="E523" t="inlineStr"/>
+      <c r="F523" t="inlineStr"/>
+      <c r="G523" t="inlineStr"/>
+      <c r="H523" t="inlineStr"/>
+      <c r="I523" t="inlineStr"/>
+      <c r="J523" t="inlineStr"/>
+      <c r="K523" t="n">
+        <v>1</v>
+      </c>
+      <c r="L523" t="inlineStr"/>
+      <c r="M523" t="inlineStr"/>
+      <c r="N523" t="inlineStr"/>
+      <c r="O523" t="inlineStr"/>
+      <c r="P523" t="inlineStr"/>
+      <c r="Q523" t="inlineStr"/>
+      <c r="R523" t="inlineStr"/>
+      <c r="S523" t="inlineStr"/>
+      <c r="T523" t="inlineStr"/>
+      <c r="U523" t="inlineStr"/>
+      <c r="V523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Ganaur City SO</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>13110101</v>
+      </c>
+      <c r="C524" t="inlineStr"/>
+      <c r="D524" t="inlineStr"/>
+      <c r="E524" t="inlineStr"/>
+      <c r="F524" t="inlineStr"/>
+      <c r="G524" t="inlineStr"/>
+      <c r="H524" t="inlineStr"/>
+      <c r="I524" t="inlineStr"/>
+      <c r="J524" t="inlineStr"/>
+      <c r="K524" t="n">
+        <v>5</v>
+      </c>
+      <c r="L524" t="inlineStr"/>
+      <c r="M524" t="inlineStr"/>
+      <c r="N524" t="inlineStr"/>
+      <c r="O524" t="inlineStr"/>
+      <c r="P524" t="inlineStr"/>
+      <c r="Q524" t="inlineStr"/>
+      <c r="R524" t="inlineStr"/>
+      <c r="S524" t="inlineStr"/>
+      <c r="T524" t="inlineStr"/>
+      <c r="U524" t="inlineStr"/>
+      <c r="V524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Ganaur SO</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>13110102</v>
+      </c>
+      <c r="C525" t="inlineStr"/>
+      <c r="D525" t="inlineStr"/>
+      <c r="E525" t="inlineStr"/>
+      <c r="F525" t="inlineStr"/>
+      <c r="G525" t="inlineStr"/>
+      <c r="H525" t="inlineStr"/>
+      <c r="I525" t="inlineStr"/>
+      <c r="J525" t="inlineStr"/>
+      <c r="K525" t="n">
+        <v>1</v>
+      </c>
+      <c r="L525" t="inlineStr"/>
+      <c r="M525" t="inlineStr"/>
+      <c r="N525" t="inlineStr"/>
+      <c r="O525" t="inlineStr"/>
+      <c r="P525" t="inlineStr"/>
+      <c r="Q525" t="inlineStr"/>
+      <c r="R525" t="inlineStr"/>
+      <c r="S525" t="inlineStr"/>
+      <c r="T525" t="inlineStr"/>
+      <c r="U525" t="inlineStr"/>
+      <c r="V525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Gohana Road SO Sonipat</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>13100104</v>
+      </c>
+      <c r="C526" t="inlineStr"/>
+      <c r="D526" t="inlineStr"/>
+      <c r="E526" t="inlineStr"/>
+      <c r="F526" t="inlineStr"/>
+      <c r="G526" t="inlineStr"/>
+      <c r="H526" t="inlineStr"/>
+      <c r="I526" t="inlineStr"/>
+      <c r="J526" t="inlineStr"/>
+      <c r="K526" t="n">
+        <v>1</v>
+      </c>
+      <c r="L526" t="inlineStr"/>
+      <c r="M526" t="inlineStr"/>
+      <c r="N526" t="inlineStr"/>
+      <c r="O526" t="inlineStr"/>
+      <c r="P526" t="inlineStr"/>
+      <c r="Q526" t="inlineStr"/>
+      <c r="R526" t="inlineStr"/>
+      <c r="S526" t="inlineStr"/>
+      <c r="T526" t="inlineStr"/>
+      <c r="U526" t="inlineStr"/>
+      <c r="V526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>HOUSING BOARD COLONY SONIPAT</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>13100105</v>
+      </c>
+      <c r="C527" t="inlineStr"/>
+      <c r="D527" t="inlineStr"/>
+      <c r="E527" t="inlineStr"/>
+      <c r="F527" t="inlineStr"/>
+      <c r="G527" t="inlineStr"/>
+      <c r="H527" t="inlineStr"/>
+      <c r="I527" t="inlineStr"/>
+      <c r="J527" t="inlineStr"/>
+      <c r="K527" t="inlineStr"/>
+      <c r="L527" t="inlineStr"/>
+      <c r="M527" t="inlineStr"/>
+      <c r="N527" t="inlineStr"/>
+      <c r="O527" t="inlineStr"/>
+      <c r="P527" t="inlineStr"/>
+      <c r="Q527" t="inlineStr"/>
+      <c r="R527" t="inlineStr"/>
+      <c r="S527" t="inlineStr"/>
+      <c r="T527" t="n">
+        <v>1</v>
+      </c>
+      <c r="U527" t="inlineStr"/>
+      <c r="V527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Joshi Chauhan B.O.</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>AO934</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Bahalgarh SO</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr"/>
+      <c r="E528" t="inlineStr"/>
+      <c r="F528" t="inlineStr"/>
+      <c r="G528" t="inlineStr"/>
+      <c r="H528" t="inlineStr"/>
+      <c r="I528" t="inlineStr"/>
+      <c r="J528" t="inlineStr"/>
+      <c r="K528" t="n">
+        <v>2</v>
+      </c>
+      <c r="L528" t="inlineStr"/>
+      <c r="M528" t="inlineStr"/>
+      <c r="N528" t="inlineStr"/>
+      <c r="O528" t="inlineStr"/>
+      <c r="P528" t="inlineStr"/>
+      <c r="Q528" t="inlineStr"/>
+      <c r="R528" t="inlineStr"/>
+      <c r="S528" t="inlineStr"/>
+      <c r="T528" t="inlineStr"/>
+      <c r="U528" t="inlineStr"/>
+      <c r="V528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Juan SO</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>13102401</v>
+      </c>
+      <c r="C529" t="inlineStr"/>
+      <c r="D529" t="inlineStr"/>
+      <c r="E529" t="inlineStr"/>
+      <c r="F529" t="inlineStr"/>
+      <c r="G529" t="inlineStr"/>
+      <c r="H529" t="inlineStr"/>
+      <c r="I529" t="n">
+        <v>1</v>
+      </c>
+      <c r="J529" t="inlineStr"/>
+      <c r="K529" t="inlineStr"/>
+      <c r="L529" t="inlineStr"/>
+      <c r="M529" t="inlineStr"/>
+      <c r="N529" t="inlineStr"/>
+      <c r="O529" t="inlineStr"/>
+      <c r="P529" t="inlineStr"/>
+      <c r="Q529" t="inlineStr"/>
+      <c r="R529" t="inlineStr"/>
+      <c r="S529" t="inlineStr"/>
+      <c r="T529" t="inlineStr"/>
+      <c r="U529" t="inlineStr"/>
+      <c r="V529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Mahra II BO</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>L8604</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Juan SO</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr"/>
+      <c r="E530" t="inlineStr"/>
+      <c r="F530" t="inlineStr"/>
+      <c r="G530" t="inlineStr"/>
+      <c r="H530" t="inlineStr"/>
+      <c r="I530" t="n">
+        <v>3</v>
+      </c>
+      <c r="J530" t="inlineStr"/>
+      <c r="K530" t="inlineStr"/>
+      <c r="L530" t="inlineStr"/>
+      <c r="M530" t="inlineStr"/>
+      <c r="N530" t="inlineStr"/>
+      <c r="O530" t="inlineStr"/>
+      <c r="P530" t="inlineStr"/>
+      <c r="Q530" t="inlineStr"/>
+      <c r="R530" t="inlineStr"/>
+      <c r="S530" t="inlineStr"/>
+      <c r="T530" t="inlineStr"/>
+      <c r="U530" t="inlineStr"/>
+      <c r="V530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Murthal SO</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>13102701</v>
+      </c>
+      <c r="C531" t="inlineStr"/>
+      <c r="D531" t="inlineStr"/>
+      <c r="E531" t="inlineStr"/>
+      <c r="F531" t="inlineStr"/>
+      <c r="G531" t="inlineStr"/>
+      <c r="H531" t="inlineStr"/>
+      <c r="I531" t="n">
+        <v>1</v>
+      </c>
+      <c r="J531" t="inlineStr"/>
+      <c r="K531" t="inlineStr"/>
+      <c r="L531" t="inlineStr"/>
+      <c r="M531" t="inlineStr"/>
+      <c r="N531" t="inlineStr"/>
+      <c r="O531" t="inlineStr"/>
+      <c r="P531" t="inlineStr"/>
+      <c r="Q531" t="inlineStr"/>
+      <c r="R531" t="inlineStr"/>
+      <c r="S531" t="inlineStr"/>
+      <c r="T531" t="inlineStr"/>
+      <c r="U531" t="inlineStr"/>
+      <c r="V531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Rohat SO Sonipat</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>13140301</v>
+      </c>
+      <c r="C532" t="inlineStr"/>
+      <c r="D532" t="inlineStr"/>
+      <c r="E532" t="inlineStr"/>
+      <c r="F532" t="inlineStr"/>
+      <c r="G532" t="inlineStr"/>
+      <c r="H532" t="inlineStr"/>
+      <c r="I532" t="n">
+        <v>2</v>
+      </c>
+      <c r="J532" t="inlineStr"/>
+      <c r="K532" t="inlineStr"/>
+      <c r="L532" t="inlineStr"/>
+      <c r="M532" t="inlineStr"/>
+      <c r="N532" t="inlineStr"/>
+      <c r="O532" t="inlineStr"/>
+      <c r="P532" t="inlineStr"/>
+      <c r="Q532" t="inlineStr"/>
+      <c r="R532" t="inlineStr"/>
+      <c r="S532" t="inlineStr"/>
+      <c r="T532" t="inlineStr"/>
+      <c r="U532" t="inlineStr"/>
+      <c r="V532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Sheikhpura BO</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>E1661</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Ganaur SO</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr"/>
+      <c r="E533" t="inlineStr"/>
+      <c r="F533" t="inlineStr"/>
+      <c r="G533" t="inlineStr"/>
+      <c r="H533" t="inlineStr"/>
+      <c r="I533" t="inlineStr"/>
+      <c r="J533" t="inlineStr"/>
+      <c r="K533" t="n">
+        <v>2</v>
+      </c>
+      <c r="L533" t="inlineStr"/>
+      <c r="M533" t="inlineStr"/>
+      <c r="N533" t="inlineStr"/>
+      <c r="O533" t="inlineStr"/>
+      <c r="P533" t="inlineStr"/>
+      <c r="Q533" t="inlineStr"/>
+      <c r="R533" t="inlineStr"/>
+      <c r="S533" t="inlineStr"/>
+      <c r="T533" t="inlineStr"/>
+      <c r="U533" t="inlineStr"/>
+      <c r="V533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Sonipat Kty SO</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>13100110</v>
+      </c>
+      <c r="C534" t="inlineStr"/>
+      <c r="D534" t="inlineStr"/>
+      <c r="E534" t="inlineStr"/>
+      <c r="F534" t="inlineStr"/>
+      <c r="G534" t="inlineStr"/>
+      <c r="H534" t="inlineStr"/>
+      <c r="I534" t="n">
+        <v>1</v>
+      </c>
+      <c r="J534" t="inlineStr"/>
+      <c r="K534" t="inlineStr"/>
+      <c r="L534" t="inlineStr"/>
+      <c r="M534" t="inlineStr"/>
+      <c r="N534" t="inlineStr"/>
+      <c r="O534" t="inlineStr"/>
+      <c r="P534" t="inlineStr"/>
+      <c r="Q534" t="inlineStr"/>
+      <c r="R534" t="inlineStr"/>
+      <c r="S534" t="inlineStr"/>
+      <c r="T534" t="inlineStr"/>
+      <c r="U534" t="inlineStr"/>
+      <c r="V534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Sonipat Mandi SO</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>13100111</v>
+      </c>
+      <c r="C535" t="inlineStr"/>
+      <c r="D535" t="inlineStr"/>
+      <c r="E535" t="inlineStr"/>
+      <c r="F535" t="inlineStr"/>
+      <c r="G535" t="inlineStr"/>
+      <c r="H535" t="inlineStr"/>
+      <c r="I535" t="inlineStr"/>
+      <c r="J535" t="inlineStr"/>
+      <c r="K535" t="n">
+        <v>1</v>
+      </c>
+      <c r="L535" t="inlineStr"/>
+      <c r="M535" t="inlineStr"/>
+      <c r="N535" t="inlineStr"/>
+      <c r="O535" t="inlineStr"/>
+      <c r="P535" t="inlineStr"/>
+      <c r="Q535" t="inlineStr"/>
+      <c r="R535" t="inlineStr"/>
+      <c r="S535" t="inlineStr"/>
+      <c r="T535" t="inlineStr"/>
+      <c r="U535" t="inlineStr"/>
+      <c r="V535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Sonipat Sector 14 SO</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>13100112</v>
+      </c>
+      <c r="C536" t="inlineStr"/>
+      <c r="D536" t="inlineStr"/>
+      <c r="E536" t="inlineStr"/>
+      <c r="F536" t="inlineStr"/>
+      <c r="G536" t="inlineStr"/>
+      <c r="H536" t="inlineStr"/>
+      <c r="I536" t="inlineStr"/>
+      <c r="J536" t="inlineStr"/>
+      <c r="K536" t="n">
+        <v>1</v>
+      </c>
+      <c r="L536" t="inlineStr"/>
+      <c r="M536" t="inlineStr"/>
+      <c r="N536" t="inlineStr"/>
+      <c r="O536" t="inlineStr"/>
+      <c r="P536" t="inlineStr"/>
+      <c r="Q536" t="inlineStr"/>
+      <c r="R536" t="inlineStr"/>
+      <c r="S536" t="inlineStr"/>
+      <c r="T536" t="n">
+        <v>1</v>
+      </c>
+      <c r="U536" t="inlineStr"/>
+      <c r="V536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
           <t>Total:</t>
         </is>
       </c>
-      <c r="B519" t="inlineStr"/>
-      <c r="C519" t="inlineStr"/>
-      <c r="D519" t="n">
-        <v>0</v>
-      </c>
-      <c r="E519" t="n">
-        <v>0</v>
-      </c>
-      <c r="F519" t="n">
-        <v>0</v>
-      </c>
-      <c r="G519" t="n">
-        <v>0</v>
-      </c>
-      <c r="H519" t="n">
-        <v>0</v>
-      </c>
-      <c r="I519" t="n">
+      <c r="B537" t="inlineStr"/>
+      <c r="C537" t="inlineStr"/>
+      <c r="D537" t="n">
+        <v>0</v>
+      </c>
+      <c r="E537" t="n">
+        <v>0</v>
+      </c>
+      <c r="F537" t="n">
+        <v>0</v>
+      </c>
+      <c r="G537" t="n">
+        <v>0</v>
+      </c>
+      <c r="H537" t="n">
+        <v>0</v>
+      </c>
+      <c r="I537" t="n">
         <v>8</v>
       </c>
-      <c r="J519" t="n">
-        <v>0</v>
-      </c>
-      <c r="K519" t="n">
+      <c r="J537" t="n">
+        <v>0</v>
+      </c>
+      <c r="K537" t="n">
         <v>18</v>
       </c>
-      <c r="L519" t="n">
-        <v>0</v>
-      </c>
-      <c r="M519" t="n">
-        <v>0</v>
-      </c>
-      <c r="N519" t="n">
-        <v>0</v>
-      </c>
-      <c r="O519" t="n">
-        <v>0</v>
-      </c>
-      <c r="P519" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q519" t="n">
-        <v>0</v>
-      </c>
-      <c r="R519" t="n">
-        <v>0</v>
-      </c>
-      <c r="S519" t="n">
-        <v>0</v>
-      </c>
-      <c r="T519" t="n">
+      <c r="L537" t="n">
+        <v>0</v>
+      </c>
+      <c r="M537" t="n">
+        <v>0</v>
+      </c>
+      <c r="N537" t="n">
+        <v>0</v>
+      </c>
+      <c r="O537" t="n">
+        <v>0</v>
+      </c>
+      <c r="P537" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q537" t="n">
+        <v>0</v>
+      </c>
+      <c r="R537" t="n">
+        <v>0</v>
+      </c>
+      <c r="S537" t="n">
+        <v>0</v>
+      </c>
+      <c r="T537" t="n">
         <v>2</v>
       </c>
-      <c r="U519" t="n">
-        <v>0</v>
-      </c>
-      <c r="V519" t="n">
+      <c r="U537" t="n">
+        <v>0</v>
+      </c>
+      <c r="V537" t="n">
         <v>0</v>
       </c>
     </row>
